--- a/artfynd/A 38082-2024 artfynd.xlsx
+++ b/artfynd/A 38082-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120448290</v>
+        <v>120448305</v>
       </c>
       <c r="B2" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446532</v>
+        <v>446347</v>
       </c>
       <c r="R2" t="n">
-        <v>6997179</v>
+        <v>6997159</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120448283</v>
+        <v>120448246</v>
       </c>
       <c r="B3" t="n">
-        <v>57341</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446809</v>
+        <v>446441</v>
       </c>
       <c r="R3" t="n">
-        <v>6997041</v>
+        <v>6997402</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120448257</v>
+        <v>120448287</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446699</v>
+        <v>446425</v>
       </c>
       <c r="R4" t="n">
-        <v>6997073</v>
+        <v>6997299</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120448304</v>
+        <v>120448236</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446383</v>
+        <v>446454</v>
       </c>
       <c r="R5" t="n">
-        <v>6997172</v>
+        <v>6997366</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120448233</v>
+        <v>120448292</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446364</v>
+        <v>446681</v>
       </c>
       <c r="R6" t="n">
-        <v>6997405</v>
+        <v>6997178</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120448259</v>
+        <v>120448249</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446616</v>
+        <v>446429</v>
       </c>
       <c r="R7" t="n">
-        <v>6997099</v>
+        <v>6997196</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120448291</v>
+        <v>120448254</v>
       </c>
       <c r="B8" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446600</v>
+        <v>446704</v>
       </c>
       <c r="R8" t="n">
-        <v>6997166</v>
+        <v>6997139</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,6 +1378,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120448258</v>
+        <v>120448248</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1444,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446658</v>
+        <v>446537</v>
       </c>
       <c r="R9" t="n">
-        <v>6997074</v>
+        <v>6997277</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,7 +1489,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120448249</v>
+        <v>120448243</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1551,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446429</v>
+        <v>446350</v>
       </c>
       <c r="R10" t="n">
-        <v>6997196</v>
+        <v>6997490</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120448231</v>
+        <v>120448232</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>91272</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,25 +1635,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446466</v>
+        <v>446646</v>
       </c>
       <c r="R11" t="n">
-        <v>6997357</v>
+        <v>6997096</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120448237</v>
+        <v>120448304</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446537</v>
+        <v>446383</v>
       </c>
       <c r="R12" t="n">
-        <v>6997341</v>
+        <v>6997172</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,11 +1801,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120448239</v>
+        <v>120448289</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446453</v>
+        <v>446427</v>
       </c>
       <c r="R13" t="n">
-        <v>6997315</v>
+        <v>6997437</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,11 +1903,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120448245</v>
+        <v>120448231</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1945,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446402</v>
+        <v>446466</v>
       </c>
       <c r="R14" t="n">
-        <v>6997470</v>
+        <v>6997357</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,11 +2005,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,7 +2031,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120448255</v>
+        <v>120448244</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2081,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446744</v>
+        <v>446358</v>
       </c>
       <c r="R15" t="n">
-        <v>6997102</v>
+        <v>6997469</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,7 +2111,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,7 +2138,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120448267</v>
+        <v>120448239</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2188,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446448</v>
+        <v>446453</v>
       </c>
       <c r="R16" t="n">
-        <v>6997133</v>
+        <v>6997315</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2255,7 +2245,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120448272</v>
+        <v>120448263</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2295,10 +2285,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446301</v>
+        <v>446583</v>
       </c>
       <c r="R17" t="n">
-        <v>6997158</v>
+        <v>6997051</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2362,10 +2352,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120448232</v>
+        <v>120448275</v>
       </c>
       <c r="B18" t="n">
-        <v>91272</v>
+        <v>57473</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2374,25 +2364,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2405,7 +2395,7 @@
         <v>446646</v>
       </c>
       <c r="R18" t="n">
-        <v>6997096</v>
+        <v>6997094</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,6 +2428,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,10 +2459,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120448246</v>
+        <v>120448288</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2480,21 +2475,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446441</v>
+        <v>446336</v>
       </c>
       <c r="R19" t="n">
-        <v>6997402</v>
+        <v>6997477</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,11 +2535,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,10 +2561,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120448275</v>
+        <v>120448266</v>
       </c>
       <c r="B20" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,21 +2577,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2611,10 +2601,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446646</v>
+        <v>446452</v>
       </c>
       <c r="R20" t="n">
-        <v>6997094</v>
+        <v>6997136</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,7 +2641,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,10 +2668,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120448299</v>
+        <v>120448251</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2694,21 +2684,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2718,10 +2708,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446445</v>
+        <v>446548</v>
       </c>
       <c r="R21" t="n">
-        <v>6997400</v>
+        <v>6997138</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2754,6 +2744,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2780,7 +2775,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120448242</v>
+        <v>120448272</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2823,7 +2818,7 @@
         <v>446301</v>
       </c>
       <c r="R22" t="n">
-        <v>6997407</v>
+        <v>6997158</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2887,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120448278</v>
+        <v>120448282</v>
       </c>
       <c r="B23" t="n">
-        <v>90864</v>
+        <v>57341</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2899,25 +2894,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100110</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2927,10 +2922,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446466</v>
+        <v>446561</v>
       </c>
       <c r="R23" t="n">
-        <v>6997354</v>
+        <v>6997196</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2989,10 +2984,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120448244</v>
+        <v>120448296</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3005,21 +3000,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3029,10 +3024,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446358</v>
+        <v>446569</v>
       </c>
       <c r="R24" t="n">
-        <v>6997469</v>
+        <v>6997072</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3065,11 +3060,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3096,10 +3086,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120448234</v>
+        <v>120448285</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3112,21 +3102,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3136,10 +3126,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446347</v>
+        <v>446490</v>
       </c>
       <c r="R25" t="n">
-        <v>6997438</v>
+        <v>6997339</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3172,11 +3162,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3203,7 +3188,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120448300</v>
+        <v>120448303</v>
       </c>
       <c r="B26" t="n">
         <v>78542</v>
@@ -3243,10 +3228,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446471</v>
+        <v>446788</v>
       </c>
       <c r="R26" t="n">
-        <v>6997266</v>
+        <v>6997029</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3305,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120448243</v>
+        <v>120448300</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3321,21 +3306,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3345,10 +3330,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446350</v>
+        <v>446471</v>
       </c>
       <c r="R27" t="n">
-        <v>6997490</v>
+        <v>6997266</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3381,11 +3366,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3412,10 +3392,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120448286</v>
+        <v>120448233</v>
       </c>
       <c r="B28" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3428,21 +3408,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3452,10 +3432,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446438</v>
+        <v>446364</v>
       </c>
       <c r="R28" t="n">
-        <v>6997300</v>
+        <v>6997405</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3488,6 +3468,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3514,10 +3499,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120448294</v>
+        <v>120448256</v>
       </c>
       <c r="B29" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3530,21 +3515,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3554,10 +3539,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446688</v>
+        <v>446770</v>
       </c>
       <c r="R29" t="n">
-        <v>6997158</v>
+        <v>6997084</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3590,6 +3575,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3616,10 +3606,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120448287</v>
+        <v>120448241</v>
       </c>
       <c r="B30" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3632,21 +3622,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3656,10 +3646,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446425</v>
+        <v>446367</v>
       </c>
       <c r="R30" t="n">
-        <v>6997299</v>
+        <v>6997300</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3692,6 +3682,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3718,10 +3713,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120448295</v>
+        <v>120448298</v>
       </c>
       <c r="B31" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3734,21 +3729,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3758,10 +3753,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446611</v>
+        <v>446309</v>
       </c>
       <c r="R31" t="n">
-        <v>6997105</v>
+        <v>6997481</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3820,7 +3815,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120448266</v>
+        <v>120448255</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -3860,10 +3855,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446452</v>
+        <v>446744</v>
       </c>
       <c r="R32" t="n">
-        <v>6997136</v>
+        <v>6997102</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3927,10 +3922,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120448303</v>
+        <v>120448234</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3943,21 +3938,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3967,10 +3962,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446788</v>
+        <v>446347</v>
       </c>
       <c r="R33" t="n">
-        <v>6997029</v>
+        <v>6997438</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4003,6 +3998,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4029,10 +4029,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120448248</v>
+        <v>120448286</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4045,21 +4045,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446537</v>
+        <v>446438</v>
       </c>
       <c r="R34" t="n">
-        <v>6997277</v>
+        <v>6997300</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4105,11 +4105,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4136,7 +4131,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120448292</v>
+        <v>120448291</v>
       </c>
       <c r="B35" t="n">
         <v>90598</v>
@@ -4176,10 +4171,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446681</v>
+        <v>446600</v>
       </c>
       <c r="R35" t="n">
-        <v>6997178</v>
+        <v>6997166</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4238,10 +4233,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120448302</v>
+        <v>120448294</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4254,21 +4249,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4278,10 +4273,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446778</v>
+        <v>446688</v>
       </c>
       <c r="R36" t="n">
-        <v>6997056</v>
+        <v>6997158</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4314,11 +4309,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4345,10 +4335,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120448256</v>
+        <v>120448290</v>
       </c>
       <c r="B37" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4361,21 +4351,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4385,10 +4375,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446770</v>
+        <v>446532</v>
       </c>
       <c r="R37" t="n">
-        <v>6997084</v>
+        <v>6997179</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4421,11 +4411,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4452,10 +4437,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120448270</v>
+        <v>120448299</v>
       </c>
       <c r="B38" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4468,21 +4453,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4492,10 +4477,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446366</v>
+        <v>446445</v>
       </c>
       <c r="R38" t="n">
-        <v>6997164</v>
+        <v>6997400</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4528,11 +4513,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4559,7 +4539,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120448236</v>
+        <v>120448267</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4599,10 +4579,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>446454</v>
+        <v>446448</v>
       </c>
       <c r="R39" t="n">
-        <v>6997366</v>
+        <v>6997133</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4666,7 +4646,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120448254</v>
+        <v>120448242</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4706,10 +4686,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>446704</v>
+        <v>446301</v>
       </c>
       <c r="R40" t="n">
-        <v>6997139</v>
+        <v>6997407</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4773,10 +4753,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120448288</v>
+        <v>120448302</v>
       </c>
       <c r="B41" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4789,21 +4769,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4813,10 +4793,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446336</v>
+        <v>446778</v>
       </c>
       <c r="R41" t="n">
-        <v>6997477</v>
+        <v>6997056</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4849,6 +4829,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4875,10 +4860,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120448274</v>
+        <v>120448278</v>
       </c>
       <c r="B42" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4891,21 +4876,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4915,10 +4900,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>446287</v>
+        <v>446466</v>
       </c>
       <c r="R42" t="n">
-        <v>6997154</v>
+        <v>6997354</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4951,11 +4936,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4982,7 +4962,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120448247</v>
+        <v>120448237</v>
       </c>
       <c r="B43" t="n">
         <v>57320</v>
@@ -5022,10 +5002,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446490</v>
+        <v>446537</v>
       </c>
       <c r="R43" t="n">
-        <v>6997390</v>
+        <v>6997341</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5089,10 +5069,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120448263</v>
+        <v>120448281</v>
       </c>
       <c r="B44" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5101,20 +5081,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5129,10 +5109,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446583</v>
+        <v>446482</v>
       </c>
       <c r="R44" t="n">
-        <v>6997051</v>
+        <v>6997150</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5165,11 +5145,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5196,7 +5171,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120448253</v>
+        <v>120448257</v>
       </c>
       <c r="B45" t="n">
         <v>57320</v>
@@ -5236,10 +5211,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446684</v>
+        <v>446699</v>
       </c>
       <c r="R45" t="n">
-        <v>6997177</v>
+        <v>6997073</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5276,7 +5251,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5303,10 +5278,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120448282</v>
+        <v>120448274</v>
       </c>
       <c r="B46" t="n">
-        <v>57341</v>
+        <v>57320</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5315,25 +5290,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5343,10 +5318,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>446561</v>
+        <v>446287</v>
       </c>
       <c r="R46" t="n">
-        <v>6997196</v>
+        <v>6997154</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5379,6 +5354,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5405,7 +5385,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120448241</v>
+        <v>120448245</v>
       </c>
       <c r="B47" t="n">
         <v>57320</v>
@@ -5445,10 +5425,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>446367</v>
+        <v>446402</v>
       </c>
       <c r="R47" t="n">
-        <v>6997300</v>
+        <v>6997470</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5512,10 +5492,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120448289</v>
+        <v>120448283</v>
       </c>
       <c r="B48" t="n">
-        <v>90598</v>
+        <v>57341</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5524,25 +5504,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100110</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5552,10 +5532,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>446427</v>
+        <v>446809</v>
       </c>
       <c r="R48" t="n">
-        <v>6997437</v>
+        <v>6997041</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5614,7 +5594,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120448240</v>
+        <v>120448258</v>
       </c>
       <c r="B49" t="n">
         <v>57320</v>
@@ -5654,10 +5634,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>446404</v>
+        <v>446658</v>
       </c>
       <c r="R49" t="n">
-        <v>6997319</v>
+        <v>6997074</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5694,7 +5674,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5721,10 +5701,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120448305</v>
+        <v>120448247</v>
       </c>
       <c r="B50" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5737,21 +5717,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5761,10 +5741,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>446347</v>
+        <v>446490</v>
       </c>
       <c r="R50" t="n">
-        <v>6997159</v>
+        <v>6997390</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5797,6 +5777,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5823,10 +5808,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120448273</v>
+        <v>120448295</v>
       </c>
       <c r="B51" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5839,21 +5824,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5863,10 +5848,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>446289</v>
+        <v>446611</v>
       </c>
       <c r="R51" t="n">
-        <v>6997154</v>
+        <v>6997105</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5899,11 +5884,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5930,7 +5910,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120448251</v>
+        <v>120448253</v>
       </c>
       <c r="B52" t="n">
         <v>57320</v>
@@ -5970,10 +5950,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>446548</v>
+        <v>446684</v>
       </c>
       <c r="R52" t="n">
-        <v>6997138</v>
+        <v>6997177</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6010,7 +5990,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6037,10 +6017,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120448306</v>
+        <v>120448270</v>
       </c>
       <c r="B53" t="n">
-        <v>57270</v>
+        <v>57320</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6049,20 +6029,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6077,10 +6057,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>446194</v>
+        <v>446366</v>
       </c>
       <c r="R53" t="n">
-        <v>6997241</v>
+        <v>6997164</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6117,7 +6097,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>nyttjar bohål i tall, ca 3 m upp.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6144,10 +6124,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120448296</v>
+        <v>120448273</v>
       </c>
       <c r="B54" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6160,21 +6140,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6184,10 +6164,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446569</v>
+        <v>446289</v>
       </c>
       <c r="R54" t="n">
-        <v>6997072</v>
+        <v>6997154</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6220,6 +6200,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6246,10 +6231,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120448281</v>
+        <v>120448240</v>
       </c>
       <c r="B55" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6258,20 +6243,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6286,10 +6271,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446482</v>
+        <v>446404</v>
       </c>
       <c r="R55" t="n">
-        <v>6997150</v>
+        <v>6997319</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6322,6 +6307,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6348,10 +6338,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120448298</v>
+        <v>120448261</v>
       </c>
       <c r="B56" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6364,21 +6354,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6388,10 +6378,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446309</v>
+        <v>446602</v>
       </c>
       <c r="R56" t="n">
-        <v>6997481</v>
+        <v>6997097</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6424,6 +6414,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6450,7 +6445,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120448269</v>
+        <v>120448259</v>
       </c>
       <c r="B57" t="n">
         <v>57320</v>
@@ -6490,10 +6485,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>446425</v>
+        <v>446616</v>
       </c>
       <c r="R57" t="n">
-        <v>6997128</v>
+        <v>6997099</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6557,7 +6552,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120448261</v>
+        <v>120448265</v>
       </c>
       <c r="B58" t="n">
         <v>57320</v>
@@ -6597,10 +6592,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>446602</v>
+        <v>446532</v>
       </c>
       <c r="R58" t="n">
-        <v>6997097</v>
+        <v>6997086</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6664,10 +6659,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120448297</v>
+        <v>120448269</v>
       </c>
       <c r="B59" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6680,21 +6675,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6704,10 +6699,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>446370</v>
+        <v>446425</v>
       </c>
       <c r="R59" t="n">
-        <v>6997167</v>
+        <v>6997128</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6740,6 +6735,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6766,10 +6766,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120448265</v>
+        <v>120448297</v>
       </c>
       <c r="B60" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6782,21 +6782,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>446532</v>
+        <v>446370</v>
       </c>
       <c r="R60" t="n">
-        <v>6997086</v>
+        <v>6997167</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6842,11 +6842,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6873,10 +6868,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120448285</v>
+        <v>120448306</v>
       </c>
       <c r="B61" t="n">
-        <v>90598</v>
+        <v>57270</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6885,38 +6880,50 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>102621</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stormyren NV, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>446490</v>
+        <v>446194</v>
       </c>
       <c r="R61" t="n">
-        <v>6997339</v>
+        <v>6997241</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6949,6 +6956,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>nyttjar bohål i tall, ca 3 m upp.</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 38082-2024 artfynd.xlsx
+++ b/artfynd/A 38082-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120448246</v>
+        <v>120448278</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446441</v>
+        <v>446466</v>
       </c>
       <c r="R3" t="n">
-        <v>6997402</v>
+        <v>6997354</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120448287</v>
+        <v>120448259</v>
       </c>
       <c r="B4" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446425</v>
+        <v>446616</v>
       </c>
       <c r="R4" t="n">
-        <v>6997299</v>
+        <v>6997099</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120448236</v>
+        <v>120448300</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446454</v>
+        <v>446471</v>
       </c>
       <c r="R5" t="n">
-        <v>6997366</v>
+        <v>6997266</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120448292</v>
+        <v>120448295</v>
       </c>
       <c r="B6" t="n">
         <v>90598</v>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446681</v>
+        <v>446611</v>
       </c>
       <c r="R6" t="n">
-        <v>6997178</v>
+        <v>6997105</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120448249</v>
+        <v>120448287</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446429</v>
+        <v>446425</v>
       </c>
       <c r="R7" t="n">
-        <v>6997196</v>
+        <v>6997299</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120448254</v>
+        <v>120448237</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1342,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446704</v>
+        <v>446537</v>
       </c>
       <c r="R8" t="n">
-        <v>6997139</v>
+        <v>6997341</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120448248</v>
+        <v>120448234</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1449,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446537</v>
+        <v>446347</v>
       </c>
       <c r="R9" t="n">
-        <v>6997277</v>
+        <v>6997438</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120448243</v>
+        <v>120448257</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1556,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446350</v>
+        <v>446699</v>
       </c>
       <c r="R10" t="n">
-        <v>6997490</v>
+        <v>6997073</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1586,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120448232</v>
+        <v>120448261</v>
       </c>
       <c r="B11" t="n">
-        <v>91272</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1635,25 +1625,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446646</v>
+        <v>446602</v>
       </c>
       <c r="R11" t="n">
-        <v>6997096</v>
+        <v>6997097</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,6 +1689,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120448304</v>
+        <v>120448248</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446383</v>
+        <v>446537</v>
       </c>
       <c r="R12" t="n">
-        <v>6997172</v>
+        <v>6997277</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,6 +1796,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,7 +1827,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120448289</v>
+        <v>120448285</v>
       </c>
       <c r="B13" t="n">
         <v>90598</v>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446427</v>
+        <v>446490</v>
       </c>
       <c r="R13" t="n">
-        <v>6997437</v>
+        <v>6997339</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120448231</v>
+        <v>120448291</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446466</v>
+        <v>446600</v>
       </c>
       <c r="R14" t="n">
-        <v>6997357</v>
+        <v>6997166</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120448244</v>
+        <v>120448290</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,21 +2047,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446358</v>
+        <v>446532</v>
       </c>
       <c r="R15" t="n">
-        <v>6997469</v>
+        <v>6997179</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,11 +2107,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2138,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120448239</v>
+        <v>120448281</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2150,20 +2145,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2178,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446453</v>
+        <v>446482</v>
       </c>
       <c r="R16" t="n">
-        <v>6997315</v>
+        <v>6997150</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,11 +2209,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2245,7 +2235,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120448263</v>
+        <v>120448239</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2285,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446583</v>
+        <v>446453</v>
       </c>
       <c r="R17" t="n">
-        <v>6997051</v>
+        <v>6997315</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2352,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120448275</v>
+        <v>120448267</v>
       </c>
       <c r="B18" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2368,21 +2358,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2382,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446646</v>
+        <v>446448</v>
       </c>
       <c r="R18" t="n">
-        <v>6997094</v>
+        <v>6997133</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2432,7 +2422,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2459,7 +2449,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120448288</v>
+        <v>120448296</v>
       </c>
       <c r="B19" t="n">
         <v>90598</v>
@@ -2499,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446336</v>
+        <v>446569</v>
       </c>
       <c r="R19" t="n">
-        <v>6997477</v>
+        <v>6997072</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2561,7 +2551,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120448266</v>
+        <v>120448249</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2601,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446452</v>
+        <v>446429</v>
       </c>
       <c r="R20" t="n">
-        <v>6997136</v>
+        <v>6997196</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2668,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120448251</v>
+        <v>120448298</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2684,21 +2674,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2708,10 +2698,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446548</v>
+        <v>446309</v>
       </c>
       <c r="R21" t="n">
-        <v>6997138</v>
+        <v>6997481</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,11 +2734,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2775,7 +2760,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120448272</v>
+        <v>120448233</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2815,10 +2800,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446301</v>
+        <v>446364</v>
       </c>
       <c r="R22" t="n">
-        <v>6997158</v>
+        <v>6997405</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2882,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120448282</v>
+        <v>120448240</v>
       </c>
       <c r="B23" t="n">
-        <v>57341</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2894,25 +2879,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2922,10 +2907,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446561</v>
+        <v>446404</v>
       </c>
       <c r="R23" t="n">
-        <v>6997196</v>
+        <v>6997319</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2958,6 +2943,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2984,10 +2974,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120448296</v>
+        <v>120448275</v>
       </c>
       <c r="B24" t="n">
-        <v>90598</v>
+        <v>57473</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3000,21 +2990,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3024,10 +3014,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446569</v>
+        <v>446646</v>
       </c>
       <c r="R24" t="n">
-        <v>6997072</v>
+        <v>6997094</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3060,6 +3050,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3086,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120448285</v>
+        <v>120448231</v>
       </c>
       <c r="B25" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3102,21 +3097,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3126,10 +3121,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446490</v>
+        <v>446466</v>
       </c>
       <c r="R25" t="n">
-        <v>6997339</v>
+        <v>6997357</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3188,10 +3183,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120448303</v>
+        <v>120448297</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3204,21 +3199,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3228,10 +3223,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446788</v>
+        <v>446370</v>
       </c>
       <c r="R26" t="n">
-        <v>6997029</v>
+        <v>6997167</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3290,7 +3285,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120448300</v>
+        <v>120448299</v>
       </c>
       <c r="B27" t="n">
         <v>78542</v>
@@ -3330,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446471</v>
+        <v>446445</v>
       </c>
       <c r="R27" t="n">
-        <v>6997266</v>
+        <v>6997400</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3392,7 +3387,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120448233</v>
+        <v>120448273</v>
       </c>
       <c r="B28" t="n">
         <v>57320</v>
@@ -3432,10 +3427,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446364</v>
+        <v>446289</v>
       </c>
       <c r="R28" t="n">
-        <v>6997405</v>
+        <v>6997154</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,7 +3467,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3499,10 +3494,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120448256</v>
+        <v>120448292</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3515,21 +3510,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3539,10 +3534,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446770</v>
+        <v>446681</v>
       </c>
       <c r="R29" t="n">
-        <v>6997084</v>
+        <v>6997178</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3575,11 +3570,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3606,10 +3596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120448241</v>
+        <v>120448289</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3622,21 +3612,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3646,10 +3636,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446367</v>
+        <v>446427</v>
       </c>
       <c r="R30" t="n">
-        <v>6997300</v>
+        <v>6997437</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3682,11 +3672,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3713,10 +3698,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120448298</v>
+        <v>120448243</v>
       </c>
       <c r="B31" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3729,21 +3714,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3753,10 +3738,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446309</v>
+        <v>446350</v>
       </c>
       <c r="R31" t="n">
-        <v>6997481</v>
+        <v>6997490</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3789,6 +3774,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3815,10 +3805,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120448255</v>
+        <v>120448286</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3831,21 +3821,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3855,10 +3845,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446744</v>
+        <v>446438</v>
       </c>
       <c r="R32" t="n">
-        <v>6997102</v>
+        <v>6997300</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3891,11 +3881,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3922,7 +3907,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120448234</v>
+        <v>120448263</v>
       </c>
       <c r="B33" t="n">
         <v>57320</v>
@@ -3962,10 +3947,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446347</v>
+        <v>446583</v>
       </c>
       <c r="R33" t="n">
-        <v>6997438</v>
+        <v>6997051</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4029,7 +4014,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120448286</v>
+        <v>120448288</v>
       </c>
       <c r="B34" t="n">
         <v>90598</v>
@@ -4069,10 +4054,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446438</v>
+        <v>446336</v>
       </c>
       <c r="R34" t="n">
-        <v>6997300</v>
+        <v>6997477</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4131,10 +4116,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120448291</v>
+        <v>120448244</v>
       </c>
       <c r="B35" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4147,21 +4132,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4171,10 +4156,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446600</v>
+        <v>446358</v>
       </c>
       <c r="R35" t="n">
-        <v>6997166</v>
+        <v>6997469</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4207,6 +4192,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4233,10 +4223,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120448294</v>
+        <v>120448304</v>
       </c>
       <c r="B36" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4249,21 +4239,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4273,10 +4263,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446688</v>
+        <v>446383</v>
       </c>
       <c r="R36" t="n">
-        <v>6997158</v>
+        <v>6997172</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4335,10 +4325,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120448290</v>
+        <v>120448253</v>
       </c>
       <c r="B37" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4351,21 +4341,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4375,10 +4365,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446532</v>
+        <v>446684</v>
       </c>
       <c r="R37" t="n">
-        <v>6997179</v>
+        <v>6997177</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4411,6 +4401,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4437,10 +4432,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120448299</v>
+        <v>120448255</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4453,21 +4448,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4477,10 +4472,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446445</v>
+        <v>446744</v>
       </c>
       <c r="R38" t="n">
-        <v>6997400</v>
+        <v>6997102</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4513,6 +4508,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4539,7 +4539,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120448267</v>
+        <v>120448251</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>446448</v>
+        <v>446548</v>
       </c>
       <c r="R39" t="n">
-        <v>6997133</v>
+        <v>6997138</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4646,10 +4646,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120448242</v>
+        <v>120448283</v>
       </c>
       <c r="B40" t="n">
-        <v>57320</v>
+        <v>57341</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4658,25 +4658,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4686,10 +4686,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>446301</v>
+        <v>446809</v>
       </c>
       <c r="R40" t="n">
-        <v>6997407</v>
+        <v>6997041</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4722,11 +4722,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4753,10 +4748,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120448302</v>
+        <v>120448294</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4769,21 +4764,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4793,10 +4788,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446778</v>
+        <v>446688</v>
       </c>
       <c r="R41" t="n">
-        <v>6997056</v>
+        <v>6997158</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4829,11 +4824,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4860,10 +4850,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120448278</v>
+        <v>120448265</v>
       </c>
       <c r="B42" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4876,21 +4866,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4900,10 +4890,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>446466</v>
+        <v>446532</v>
       </c>
       <c r="R42" t="n">
-        <v>6997354</v>
+        <v>6997086</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4936,6 +4926,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4962,7 +4957,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120448237</v>
+        <v>120448266</v>
       </c>
       <c r="B43" t="n">
         <v>57320</v>
@@ -5002,10 +4997,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446537</v>
+        <v>446452</v>
       </c>
       <c r="R43" t="n">
-        <v>6997341</v>
+        <v>6997136</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5069,10 +5064,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120448281</v>
+        <v>120448258</v>
       </c>
       <c r="B44" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5081,20 +5076,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5109,10 +5104,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446482</v>
+        <v>446658</v>
       </c>
       <c r="R44" t="n">
-        <v>6997150</v>
+        <v>6997074</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5145,6 +5140,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5171,7 +5171,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120448257</v>
+        <v>120448246</v>
       </c>
       <c r="B45" t="n">
         <v>57320</v>
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446699</v>
+        <v>446441</v>
       </c>
       <c r="R45" t="n">
-        <v>6997073</v>
+        <v>6997402</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5278,10 +5278,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120448274</v>
+        <v>120448302</v>
       </c>
       <c r="B46" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5294,21 +5294,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>446287</v>
+        <v>446778</v>
       </c>
       <c r="R46" t="n">
-        <v>6997154</v>
+        <v>6997056</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5385,10 +5385,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120448245</v>
+        <v>120448303</v>
       </c>
       <c r="B47" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5401,21 +5401,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5425,10 +5425,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>446402</v>
+        <v>446788</v>
       </c>
       <c r="R47" t="n">
-        <v>6997470</v>
+        <v>6997029</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5461,11 +5461,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5492,10 +5487,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120448283</v>
+        <v>120448256</v>
       </c>
       <c r="B48" t="n">
-        <v>57341</v>
+        <v>57320</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5504,25 +5499,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5532,10 +5527,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>446809</v>
+        <v>446770</v>
       </c>
       <c r="R48" t="n">
-        <v>6997041</v>
+        <v>6997084</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5568,6 +5563,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5594,7 +5594,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120448258</v>
+        <v>120448241</v>
       </c>
       <c r="B49" t="n">
         <v>57320</v>
@@ -5634,10 +5634,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>446658</v>
+        <v>446367</v>
       </c>
       <c r="R49" t="n">
-        <v>6997074</v>
+        <v>6997300</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5701,7 +5701,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120448247</v>
+        <v>120448270</v>
       </c>
       <c r="B50" t="n">
         <v>57320</v>
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>446490</v>
+        <v>446366</v>
       </c>
       <c r="R50" t="n">
-        <v>6997390</v>
+        <v>6997164</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5808,10 +5808,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120448295</v>
+        <v>120448242</v>
       </c>
       <c r="B51" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5824,21 +5824,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>446611</v>
+        <v>446301</v>
       </c>
       <c r="R51" t="n">
-        <v>6997105</v>
+        <v>6997407</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5884,6 +5884,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5910,7 +5915,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120448253</v>
+        <v>120448272</v>
       </c>
       <c r="B52" t="n">
         <v>57320</v>
@@ -5950,10 +5955,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>446684</v>
+        <v>446301</v>
       </c>
       <c r="R52" t="n">
-        <v>6997177</v>
+        <v>6997158</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5990,7 +5995,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6017,7 +6022,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120448270</v>
+        <v>120448274</v>
       </c>
       <c r="B53" t="n">
         <v>57320</v>
@@ -6057,10 +6062,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>446366</v>
+        <v>446287</v>
       </c>
       <c r="R53" t="n">
-        <v>6997164</v>
+        <v>6997154</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6097,7 +6102,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6124,10 +6129,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120448273</v>
+        <v>120448282</v>
       </c>
       <c r="B54" t="n">
-        <v>57320</v>
+        <v>57341</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6136,25 +6141,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6164,10 +6169,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446289</v>
+        <v>446561</v>
       </c>
       <c r="R54" t="n">
-        <v>6997154</v>
+        <v>6997196</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6200,11 +6205,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6231,7 +6231,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120448240</v>
+        <v>120448254</v>
       </c>
       <c r="B55" t="n">
         <v>57320</v>
@@ -6271,10 +6271,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446404</v>
+        <v>446704</v>
       </c>
       <c r="R55" t="n">
-        <v>6997319</v>
+        <v>6997139</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6338,7 +6338,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120448261</v>
+        <v>120448247</v>
       </c>
       <c r="B56" t="n">
         <v>57320</v>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446602</v>
+        <v>446490</v>
       </c>
       <c r="R56" t="n">
-        <v>6997097</v>
+        <v>6997390</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6445,10 +6445,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120448259</v>
+        <v>120448232</v>
       </c>
       <c r="B57" t="n">
-        <v>57320</v>
+        <v>91272</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6457,25 +6457,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>446616</v>
+        <v>446646</v>
       </c>
       <c r="R57" t="n">
-        <v>6997099</v>
+        <v>6997096</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6521,11 +6521,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6552,7 +6547,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120448265</v>
+        <v>120448236</v>
       </c>
       <c r="B58" t="n">
         <v>57320</v>
@@ -6592,10 +6587,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>446532</v>
+        <v>446454</v>
       </c>
       <c r="R58" t="n">
-        <v>6997086</v>
+        <v>6997366</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6766,10 +6761,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120448297</v>
+        <v>120448245</v>
       </c>
       <c r="B60" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6782,21 +6777,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6806,10 +6801,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>446370</v>
+        <v>446402</v>
       </c>
       <c r="R60" t="n">
-        <v>6997167</v>
+        <v>6997470</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6842,6 +6837,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 38082-2024 artfynd.xlsx
+++ b/artfynd/A 38082-2024 artfynd.xlsx
@@ -1720,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120448248</v>
+        <v>120448285</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446537</v>
+        <v>446490</v>
       </c>
       <c r="R12" t="n">
-        <v>6997277</v>
+        <v>6997339</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,11 +1796,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,7 +1822,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120448285</v>
+        <v>120448291</v>
       </c>
       <c r="B13" t="n">
         <v>90598</v>
@@ -1867,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446490</v>
+        <v>446600</v>
       </c>
       <c r="R13" t="n">
-        <v>6997339</v>
+        <v>6997166</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,7 +1924,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120448291</v>
+        <v>120448290</v>
       </c>
       <c r="B14" t="n">
         <v>90598</v>
@@ -1969,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446600</v>
+        <v>446532</v>
       </c>
       <c r="R14" t="n">
-        <v>6997166</v>
+        <v>6997179</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120448290</v>
+        <v>120448248</v>
       </c>
       <c r="B15" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,21 +2042,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2071,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446532</v>
+        <v>446537</v>
       </c>
       <c r="R15" t="n">
-        <v>6997179</v>
+        <v>6997277</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,6 +2102,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2760,10 +2760,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120448233</v>
+        <v>120448231</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2776,21 +2776,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446364</v>
+        <v>446466</v>
       </c>
       <c r="R22" t="n">
-        <v>6997405</v>
+        <v>6997357</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2836,11 +2836,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2867,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120448240</v>
+        <v>120448275</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2883,21 +2878,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2907,10 +2902,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446404</v>
+        <v>446646</v>
       </c>
       <c r="R23" t="n">
-        <v>6997319</v>
+        <v>6997094</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2947,7 +2942,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2974,10 +2969,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120448275</v>
+        <v>120448233</v>
       </c>
       <c r="B24" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2990,21 +2985,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3014,10 +3009,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446646</v>
+        <v>446364</v>
       </c>
       <c r="R24" t="n">
-        <v>6997094</v>
+        <v>6997405</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3054,7 +3049,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3081,10 +3076,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120448231</v>
+        <v>120448240</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3097,21 +3092,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3121,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446466</v>
+        <v>446404</v>
       </c>
       <c r="R25" t="n">
-        <v>6997357</v>
+        <v>6997319</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3157,6 +3152,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3285,10 +3285,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120448299</v>
+        <v>120448292</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3301,21 +3301,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446445</v>
+        <v>446681</v>
       </c>
       <c r="R27" t="n">
-        <v>6997400</v>
+        <v>6997178</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3387,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120448273</v>
+        <v>120448289</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3403,21 +3403,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446289</v>
+        <v>446427</v>
       </c>
       <c r="R28" t="n">
-        <v>6997154</v>
+        <v>6997437</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3463,11 +3463,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3494,10 +3489,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120448292</v>
+        <v>120448273</v>
       </c>
       <c r="B29" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3510,21 +3505,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3534,10 +3529,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446681</v>
+        <v>446289</v>
       </c>
       <c r="R29" t="n">
-        <v>6997178</v>
+        <v>6997154</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3570,6 +3565,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3596,10 +3596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120448289</v>
+        <v>120448299</v>
       </c>
       <c r="B30" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3612,21 +3612,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446427</v>
+        <v>446445</v>
       </c>
       <c r="R30" t="n">
-        <v>6997437</v>
+        <v>6997400</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 38082-2024 artfynd.xlsx
+++ b/artfynd/A 38082-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120448305</v>
+        <v>120448299</v>
       </c>
       <c r="B2" t="n">
         <v>78542</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446347</v>
+        <v>446445</v>
       </c>
       <c r="R2" t="n">
-        <v>6997159</v>
+        <v>6997400</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120448278</v>
+        <v>120448255</v>
       </c>
       <c r="B3" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446466</v>
+        <v>446744</v>
       </c>
       <c r="R3" t="n">
-        <v>6997354</v>
+        <v>6997102</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120448259</v>
+        <v>120448278</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446616</v>
+        <v>446466</v>
       </c>
       <c r="R4" t="n">
-        <v>6997099</v>
+        <v>6997354</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120448300</v>
+        <v>120448281</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446471</v>
+        <v>446482</v>
       </c>
       <c r="R5" t="n">
-        <v>6997266</v>
+        <v>6997150</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120448295</v>
+        <v>120448296</v>
       </c>
       <c r="B6" t="n">
         <v>90598</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446611</v>
+        <v>446569</v>
       </c>
       <c r="R6" t="n">
-        <v>6997105</v>
+        <v>6997072</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120448287</v>
+        <v>120448291</v>
       </c>
       <c r="B7" t="n">
         <v>90598</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446425</v>
+        <v>446600</v>
       </c>
       <c r="R7" t="n">
-        <v>6997299</v>
+        <v>6997166</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120448237</v>
+        <v>120448263</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446537</v>
+        <v>446583</v>
       </c>
       <c r="R8" t="n">
-        <v>6997341</v>
+        <v>6997051</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120448234</v>
+        <v>120448272</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446347</v>
+        <v>446301</v>
       </c>
       <c r="R9" t="n">
-        <v>6997438</v>
+        <v>6997158</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120448257</v>
+        <v>120448261</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446699</v>
+        <v>446602</v>
       </c>
       <c r="R10" t="n">
-        <v>6997073</v>
+        <v>6997097</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,7 +1613,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120448261</v>
+        <v>120448269</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446602</v>
+        <v>446425</v>
       </c>
       <c r="R11" t="n">
-        <v>6997097</v>
+        <v>6997128</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120448285</v>
+        <v>120448247</v>
       </c>
       <c r="B12" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1763,7 +1763,7 @@
         <v>446490</v>
       </c>
       <c r="R12" t="n">
-        <v>6997339</v>
+        <v>6997390</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,6 +1796,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,7 +1827,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120448291</v>
+        <v>120448292</v>
       </c>
       <c r="B13" t="n">
         <v>90598</v>
@@ -1862,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446600</v>
+        <v>446681</v>
       </c>
       <c r="R13" t="n">
-        <v>6997166</v>
+        <v>6997178</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120448290</v>
+        <v>120448298</v>
       </c>
       <c r="B14" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,21 +1945,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446532</v>
+        <v>446309</v>
       </c>
       <c r="R14" t="n">
-        <v>6997179</v>
+        <v>6997481</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2026,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120448248</v>
+        <v>120448286</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,21 +2047,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446537</v>
+        <v>446438</v>
       </c>
       <c r="R15" t="n">
-        <v>6997277</v>
+        <v>6997300</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,11 +2107,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2133,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120448281</v>
+        <v>120448251</v>
       </c>
       <c r="B16" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2145,20 +2145,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446482</v>
+        <v>446548</v>
       </c>
       <c r="R16" t="n">
-        <v>6997150</v>
+        <v>6997138</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,6 +2209,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,7 +2240,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120448239</v>
+        <v>120448259</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2275,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446453</v>
+        <v>446616</v>
       </c>
       <c r="R17" t="n">
-        <v>6997315</v>
+        <v>6997099</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,7 +2347,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120448267</v>
+        <v>120448256</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2382,10 +2387,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446448</v>
+        <v>446770</v>
       </c>
       <c r="R18" t="n">
-        <v>6997133</v>
+        <v>6997084</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2449,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120448296</v>
+        <v>120448240</v>
       </c>
       <c r="B19" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2465,21 +2470,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2494,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446569</v>
+        <v>446404</v>
       </c>
       <c r="R19" t="n">
-        <v>6997072</v>
+        <v>6997319</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2525,6 +2530,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2551,7 +2561,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120448249</v>
+        <v>120448239</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2591,10 +2601,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446429</v>
+        <v>446453</v>
       </c>
       <c r="R20" t="n">
-        <v>6997196</v>
+        <v>6997315</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2658,10 +2668,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120448298</v>
+        <v>120448257</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2674,21 +2684,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2698,10 +2708,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446309</v>
+        <v>446699</v>
       </c>
       <c r="R21" t="n">
-        <v>6997481</v>
+        <v>6997073</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2734,6 +2744,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2760,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120448231</v>
+        <v>120448285</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2776,21 +2791,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2800,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446466</v>
+        <v>446490</v>
       </c>
       <c r="R22" t="n">
-        <v>6997357</v>
+        <v>6997339</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2862,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120448275</v>
+        <v>120448232</v>
       </c>
       <c r="B23" t="n">
-        <v>57473</v>
+        <v>91272</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2874,25 +2889,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2905,7 +2920,7 @@
         <v>446646</v>
       </c>
       <c r="R23" t="n">
-        <v>6997094</v>
+        <v>6997096</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2938,11 +2953,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2969,7 +2979,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120448233</v>
+        <v>120448241</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3009,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446364</v>
+        <v>446367</v>
       </c>
       <c r="R24" t="n">
-        <v>6997405</v>
+        <v>6997300</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3076,10 +3086,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120448240</v>
+        <v>120448282</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>57341</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3088,25 +3098,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3116,10 +3126,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446404</v>
+        <v>446561</v>
       </c>
       <c r="R25" t="n">
-        <v>6997319</v>
+        <v>6997196</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,11 +3162,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,10 +3188,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120448297</v>
+        <v>120448258</v>
       </c>
       <c r="B26" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3199,21 +3204,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3223,10 +3228,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446370</v>
+        <v>446658</v>
       </c>
       <c r="R26" t="n">
-        <v>6997167</v>
+        <v>6997074</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3259,6 +3264,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3285,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120448292</v>
+        <v>120448242</v>
       </c>
       <c r="B27" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3301,21 +3311,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3325,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446681</v>
+        <v>446301</v>
       </c>
       <c r="R27" t="n">
-        <v>6997178</v>
+        <v>6997407</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3361,6 +3371,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3489,7 +3504,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120448273</v>
+        <v>120448248</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3529,10 +3544,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446289</v>
+        <v>446537</v>
       </c>
       <c r="R29" t="n">
-        <v>6997154</v>
+        <v>6997277</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3569,7 +3584,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3596,10 +3611,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120448299</v>
+        <v>120448244</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3612,21 +3627,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3636,10 +3651,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446445</v>
+        <v>446358</v>
       </c>
       <c r="R30" t="n">
-        <v>6997400</v>
+        <v>6997469</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3672,6 +3687,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3698,7 +3718,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120448243</v>
+        <v>120448273</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3738,10 +3758,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446350</v>
+        <v>446289</v>
       </c>
       <c r="R31" t="n">
-        <v>6997490</v>
+        <v>6997154</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3778,7 +3798,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3805,10 +3825,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120448286</v>
+        <v>120448300</v>
       </c>
       <c r="B32" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3821,21 +3841,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3845,10 +3865,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446438</v>
+        <v>446471</v>
       </c>
       <c r="R32" t="n">
-        <v>6997300</v>
+        <v>6997266</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3907,7 +3927,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120448263</v>
+        <v>120448265</v>
       </c>
       <c r="B33" t="n">
         <v>57320</v>
@@ -3947,10 +3967,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446583</v>
+        <v>446532</v>
       </c>
       <c r="R33" t="n">
-        <v>6997051</v>
+        <v>6997086</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4014,10 +4034,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120448288</v>
+        <v>120448270</v>
       </c>
       <c r="B34" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4030,21 +4050,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4054,10 +4074,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446336</v>
+        <v>446366</v>
       </c>
       <c r="R34" t="n">
-        <v>6997477</v>
+        <v>6997164</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4090,6 +4110,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4116,7 +4141,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120448244</v>
+        <v>120448243</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4156,10 +4181,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446358</v>
+        <v>446350</v>
       </c>
       <c r="R35" t="n">
-        <v>6997469</v>
+        <v>6997490</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4196,7 +4221,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4432,7 +4457,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120448255</v>
+        <v>120448245</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -4472,10 +4497,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446744</v>
+        <v>446402</v>
       </c>
       <c r="R38" t="n">
-        <v>6997102</v>
+        <v>6997470</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4539,10 +4564,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120448251</v>
+        <v>120448294</v>
       </c>
       <c r="B39" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4555,21 +4580,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4579,10 +4604,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>446548</v>
+        <v>446688</v>
       </c>
       <c r="R39" t="n">
-        <v>6997138</v>
+        <v>6997158</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4615,11 +4640,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4646,10 +4666,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120448283</v>
+        <v>120448295</v>
       </c>
       <c r="B40" t="n">
-        <v>57341</v>
+        <v>90598</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4658,25 +4678,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100110</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4686,10 +4706,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>446809</v>
+        <v>446611</v>
       </c>
       <c r="R40" t="n">
-        <v>6997041</v>
+        <v>6997105</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4748,7 +4768,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120448294</v>
+        <v>120448288</v>
       </c>
       <c r="B41" t="n">
         <v>90598</v>
@@ -4788,10 +4808,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446688</v>
+        <v>446336</v>
       </c>
       <c r="R41" t="n">
-        <v>6997158</v>
+        <v>6997477</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4850,7 +4870,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120448265</v>
+        <v>120448274</v>
       </c>
       <c r="B42" t="n">
         <v>57320</v>
@@ -4890,10 +4910,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>446532</v>
+        <v>446287</v>
       </c>
       <c r="R42" t="n">
-        <v>6997086</v>
+        <v>6997154</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4957,7 +4977,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120448266</v>
+        <v>120448249</v>
       </c>
       <c r="B43" t="n">
         <v>57320</v>
@@ -4997,10 +5017,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446452</v>
+        <v>446429</v>
       </c>
       <c r="R43" t="n">
-        <v>6997136</v>
+        <v>6997196</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5064,10 +5084,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120448258</v>
+        <v>120448297</v>
       </c>
       <c r="B44" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5080,21 +5100,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5104,10 +5124,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446658</v>
+        <v>446370</v>
       </c>
       <c r="R44" t="n">
-        <v>6997074</v>
+        <v>6997167</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5140,11 +5160,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5171,10 +5186,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120448246</v>
+        <v>120448302</v>
       </c>
       <c r="B45" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5187,21 +5202,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5211,10 +5226,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446441</v>
+        <v>446778</v>
       </c>
       <c r="R45" t="n">
-        <v>6997402</v>
+        <v>6997056</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5251,7 +5266,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5278,7 +5293,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120448302</v>
+        <v>120448303</v>
       </c>
       <c r="B46" t="n">
         <v>78542</v>
@@ -5318,10 +5333,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>446778</v>
+        <v>446788</v>
       </c>
       <c r="R46" t="n">
-        <v>6997056</v>
+        <v>6997029</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5354,11 +5369,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5385,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120448303</v>
+        <v>120448287</v>
       </c>
       <c r="B47" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5401,21 +5411,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5425,10 +5435,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>446788</v>
+        <v>446425</v>
       </c>
       <c r="R47" t="n">
-        <v>6997029</v>
+        <v>6997299</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5487,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120448256</v>
+        <v>120448231</v>
       </c>
       <c r="B48" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5503,21 +5513,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5527,10 +5537,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>446770</v>
+        <v>446466</v>
       </c>
       <c r="R48" t="n">
-        <v>6997084</v>
+        <v>6997357</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5563,11 +5573,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5594,7 +5599,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120448241</v>
+        <v>120448266</v>
       </c>
       <c r="B49" t="n">
         <v>57320</v>
@@ -5634,10 +5639,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>446367</v>
+        <v>446452</v>
       </c>
       <c r="R49" t="n">
-        <v>6997300</v>
+        <v>6997136</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5701,7 +5706,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120448270</v>
+        <v>120448236</v>
       </c>
       <c r="B50" t="n">
         <v>57320</v>
@@ -5741,10 +5746,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>446366</v>
+        <v>446454</v>
       </c>
       <c r="R50" t="n">
-        <v>6997164</v>
+        <v>6997366</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5781,7 +5786,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5808,7 +5813,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120448242</v>
+        <v>120448246</v>
       </c>
       <c r="B51" t="n">
         <v>57320</v>
@@ -5848,10 +5853,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>446301</v>
+        <v>446441</v>
       </c>
       <c r="R51" t="n">
-        <v>6997407</v>
+        <v>6997402</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5915,10 +5920,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120448272</v>
+        <v>120448283</v>
       </c>
       <c r="B52" t="n">
-        <v>57320</v>
+        <v>57341</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5927,25 +5932,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5955,10 +5960,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>446301</v>
+        <v>446809</v>
       </c>
       <c r="R52" t="n">
-        <v>6997158</v>
+        <v>6997041</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5991,11 +5996,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6022,10 +6022,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120448274</v>
+        <v>120448305</v>
       </c>
       <c r="B53" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6038,21 +6038,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6062,10 +6062,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>446287</v>
+        <v>446347</v>
       </c>
       <c r="R53" t="n">
-        <v>6997154</v>
+        <v>6997159</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6098,11 +6098,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6129,10 +6124,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120448282</v>
+        <v>120448237</v>
       </c>
       <c r="B54" t="n">
-        <v>57341</v>
+        <v>57320</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6141,25 +6136,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6169,10 +6164,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446561</v>
+        <v>446537</v>
       </c>
       <c r="R54" t="n">
-        <v>6997196</v>
+        <v>6997341</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6205,6 +6200,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6231,7 +6231,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120448254</v>
+        <v>120448267</v>
       </c>
       <c r="B55" t="n">
         <v>57320</v>
@@ -6271,10 +6271,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446704</v>
+        <v>446448</v>
       </c>
       <c r="R55" t="n">
-        <v>6997139</v>
+        <v>6997133</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6338,7 +6338,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120448247</v>
+        <v>120448233</v>
       </c>
       <c r="B56" t="n">
         <v>57320</v>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446490</v>
+        <v>446364</v>
       </c>
       <c r="R56" t="n">
-        <v>6997390</v>
+        <v>6997405</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6445,10 +6445,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120448232</v>
+        <v>120448234</v>
       </c>
       <c r="B57" t="n">
-        <v>91272</v>
+        <v>57320</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6457,25 +6457,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>446646</v>
+        <v>446347</v>
       </c>
       <c r="R57" t="n">
-        <v>6997096</v>
+        <v>6997438</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6521,6 +6521,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6547,10 +6552,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120448236</v>
+        <v>120448290</v>
       </c>
       <c r="B58" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6563,21 +6568,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6587,10 +6592,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>446454</v>
+        <v>446532</v>
       </c>
       <c r="R58" t="n">
-        <v>6997366</v>
+        <v>6997179</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6623,11 +6628,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6654,7 +6654,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120448269</v>
+        <v>120448254</v>
       </c>
       <c r="B59" t="n">
         <v>57320</v>
@@ -6694,10 +6694,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>446425</v>
+        <v>446704</v>
       </c>
       <c r="R59" t="n">
-        <v>6997128</v>
+        <v>6997139</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6761,10 +6761,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120448245</v>
+        <v>120448275</v>
       </c>
       <c r="B60" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6777,21 +6777,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6801,10 +6801,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>446402</v>
+        <v>446646</v>
       </c>
       <c r="R60" t="n">
-        <v>6997470</v>
+        <v>6997094</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 38082-2024 artfynd.xlsx
+++ b/artfynd/A 38082-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120448299</v>
+        <v>120448298</v>
       </c>
       <c r="B2" t="n">
         <v>78542</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446445</v>
+        <v>446309</v>
       </c>
       <c r="R2" t="n">
-        <v>6997400</v>
+        <v>6997481</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120448255</v>
+        <v>120448272</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446744</v>
+        <v>446301</v>
       </c>
       <c r="R3" t="n">
-        <v>6997102</v>
+        <v>6997158</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120448278</v>
+        <v>120448240</v>
       </c>
       <c r="B4" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446466</v>
+        <v>446404</v>
       </c>
       <c r="R4" t="n">
-        <v>6997354</v>
+        <v>6997319</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120448281</v>
+        <v>120448258</v>
       </c>
       <c r="B5" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,20 +1003,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446482</v>
+        <v>446658</v>
       </c>
       <c r="R5" t="n">
-        <v>6997150</v>
+        <v>6997074</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120448296</v>
+        <v>120448273</v>
       </c>
       <c r="B6" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446569</v>
+        <v>446289</v>
       </c>
       <c r="R6" t="n">
-        <v>6997072</v>
+        <v>6997154</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120448291</v>
+        <v>120448248</v>
       </c>
       <c r="B7" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446600</v>
+        <v>446537</v>
       </c>
       <c r="R7" t="n">
-        <v>6997166</v>
+        <v>6997277</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120448263</v>
+        <v>120448265</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1332,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446583</v>
+        <v>446532</v>
       </c>
       <c r="R8" t="n">
-        <v>6997051</v>
+        <v>6997086</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120448272</v>
+        <v>120448267</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1439,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446301</v>
+        <v>446448</v>
       </c>
       <c r="R9" t="n">
-        <v>6997158</v>
+        <v>6997133</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120448261</v>
+        <v>120448286</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446602</v>
+        <v>446438</v>
       </c>
       <c r="R10" t="n">
-        <v>6997097</v>
+        <v>6997300</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,11 +1602,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120448269</v>
+        <v>120448289</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446425</v>
+        <v>446427</v>
       </c>
       <c r="R11" t="n">
-        <v>6997128</v>
+        <v>6997437</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,11 +1704,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120448247</v>
+        <v>120448303</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446490</v>
+        <v>446788</v>
       </c>
       <c r="R12" t="n">
-        <v>6997390</v>
+        <v>6997029</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,11 +1806,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120448292</v>
+        <v>120448305</v>
       </c>
       <c r="B13" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446681</v>
+        <v>446347</v>
       </c>
       <c r="R13" t="n">
-        <v>6997178</v>
+        <v>6997159</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120448298</v>
+        <v>120448290</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1969,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446309</v>
+        <v>446532</v>
       </c>
       <c r="R14" t="n">
-        <v>6997481</v>
+        <v>6997179</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120448286</v>
+        <v>120448236</v>
       </c>
       <c r="B15" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,21 +2052,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2071,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446438</v>
+        <v>446454</v>
       </c>
       <c r="R15" t="n">
-        <v>6997300</v>
+        <v>6997366</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,6 +2112,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2133,7 +2143,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120448251</v>
+        <v>120448257</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2173,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446548</v>
+        <v>446699</v>
       </c>
       <c r="R16" t="n">
-        <v>6997138</v>
+        <v>6997073</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2213,7 +2223,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2240,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120448259</v>
+        <v>120448295</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2256,21 +2266,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446616</v>
+        <v>446611</v>
       </c>
       <c r="R17" t="n">
-        <v>6997099</v>
+        <v>6997105</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,11 +2326,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2347,7 +2352,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120448256</v>
+        <v>120448263</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2387,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446770</v>
+        <v>446583</v>
       </c>
       <c r="R18" t="n">
-        <v>6997084</v>
+        <v>6997051</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,7 +2459,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120448240</v>
+        <v>120448249</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2494,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446404</v>
+        <v>446429</v>
       </c>
       <c r="R19" t="n">
-        <v>6997319</v>
+        <v>6997196</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2534,7 +2539,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2561,7 +2566,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120448239</v>
+        <v>120448234</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2601,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446453</v>
+        <v>446347</v>
       </c>
       <c r="R20" t="n">
-        <v>6997315</v>
+        <v>6997438</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2668,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120448257</v>
+        <v>120448285</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2684,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2708,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446699</v>
+        <v>446490</v>
       </c>
       <c r="R21" t="n">
-        <v>6997073</v>
+        <v>6997339</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,11 +2749,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2775,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120448285</v>
+        <v>120448255</v>
       </c>
       <c r="B22" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2791,21 +2791,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446490</v>
+        <v>446744</v>
       </c>
       <c r="R22" t="n">
-        <v>6997339</v>
+        <v>6997102</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2851,6 +2851,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2877,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120448232</v>
+        <v>120448241</v>
       </c>
       <c r="B23" t="n">
-        <v>91272</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2889,25 +2894,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2917,10 +2922,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446646</v>
+        <v>446367</v>
       </c>
       <c r="R23" t="n">
-        <v>6997096</v>
+        <v>6997300</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2953,6 +2958,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2979,10 +2989,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120448241</v>
+        <v>120448302</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2995,21 +3005,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3019,10 +3029,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446367</v>
+        <v>446778</v>
       </c>
       <c r="R24" t="n">
-        <v>6997300</v>
+        <v>6997056</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3059,7 +3069,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3086,10 +3096,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120448282</v>
+        <v>120448246</v>
       </c>
       <c r="B25" t="n">
-        <v>57341</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3098,25 +3108,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3126,10 +3136,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446561</v>
+        <v>446441</v>
       </c>
       <c r="R25" t="n">
-        <v>6997196</v>
+        <v>6997402</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3162,6 +3172,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3188,7 +3203,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120448258</v>
+        <v>120448251</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3228,10 +3243,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446658</v>
+        <v>446548</v>
       </c>
       <c r="R26" t="n">
-        <v>6997074</v>
+        <v>6997138</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3295,7 +3310,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120448242</v>
+        <v>120448259</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3335,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446301</v>
+        <v>446616</v>
       </c>
       <c r="R27" t="n">
-        <v>6997407</v>
+        <v>6997099</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3402,10 +3417,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120448289</v>
+        <v>120448274</v>
       </c>
       <c r="B28" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3418,21 +3433,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3442,10 +3457,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446427</v>
+        <v>446287</v>
       </c>
       <c r="R28" t="n">
-        <v>6997437</v>
+        <v>6997154</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3478,6 +3493,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3504,7 +3524,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120448248</v>
+        <v>120448247</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3544,10 +3564,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446537</v>
+        <v>446490</v>
       </c>
       <c r="R29" t="n">
-        <v>6997277</v>
+        <v>6997390</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3611,10 +3631,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120448244</v>
+        <v>120448283</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>57341</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3623,25 +3643,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3651,10 +3671,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446358</v>
+        <v>446809</v>
       </c>
       <c r="R30" t="n">
-        <v>6997469</v>
+        <v>6997041</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3687,11 +3707,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3718,10 +3733,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120448273</v>
+        <v>120448281</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3730,20 +3745,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3758,10 +3773,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446289</v>
+        <v>446482</v>
       </c>
       <c r="R31" t="n">
-        <v>6997154</v>
+        <v>6997150</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3794,11 +3809,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3825,10 +3835,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120448300</v>
+        <v>120448232</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>91272</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3837,25 +3847,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3865,10 +3875,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446471</v>
+        <v>446646</v>
       </c>
       <c r="R32" t="n">
-        <v>6997266</v>
+        <v>6997096</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3927,10 +3937,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120448265</v>
+        <v>120448291</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3943,21 +3953,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3967,10 +3977,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446532</v>
+        <v>446600</v>
       </c>
       <c r="R33" t="n">
-        <v>6997086</v>
+        <v>6997166</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4003,11 +4013,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4034,10 +4039,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120448270</v>
+        <v>120448287</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4050,21 +4055,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4074,10 +4079,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446366</v>
+        <v>446425</v>
       </c>
       <c r="R34" t="n">
-        <v>6997164</v>
+        <v>6997299</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4110,11 +4115,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4141,10 +4141,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120448243</v>
+        <v>120448288</v>
       </c>
       <c r="B35" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4157,21 +4157,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4181,10 +4181,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446350</v>
+        <v>446336</v>
       </c>
       <c r="R35" t="n">
-        <v>6997490</v>
+        <v>6997477</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4217,11 +4217,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4248,10 +4243,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120448304</v>
+        <v>120448237</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4264,21 +4259,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4288,10 +4283,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446383</v>
+        <v>446537</v>
       </c>
       <c r="R36" t="n">
-        <v>6997172</v>
+        <v>6997341</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4324,6 +4319,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4350,7 +4350,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120448253</v>
+        <v>120448239</v>
       </c>
       <c r="B37" t="n">
         <v>57320</v>
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446684</v>
+        <v>446453</v>
       </c>
       <c r="R37" t="n">
-        <v>6997177</v>
+        <v>6997315</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4457,10 +4457,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120448245</v>
+        <v>120448296</v>
       </c>
       <c r="B38" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4473,21 +4473,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4497,10 +4497,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446402</v>
+        <v>446569</v>
       </c>
       <c r="R38" t="n">
-        <v>6997470</v>
+        <v>6997072</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4533,11 +4533,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4564,10 +4559,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120448294</v>
+        <v>120448304</v>
       </c>
       <c r="B39" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4580,21 +4575,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4604,10 +4599,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>446688</v>
+        <v>446383</v>
       </c>
       <c r="R39" t="n">
-        <v>6997158</v>
+        <v>6997172</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4666,10 +4661,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120448295</v>
+        <v>120448233</v>
       </c>
       <c r="B40" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4682,21 +4677,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4706,10 +4701,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>446611</v>
+        <v>446364</v>
       </c>
       <c r="R40" t="n">
-        <v>6997105</v>
+        <v>6997405</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4742,6 +4737,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4768,10 +4768,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120448288</v>
+        <v>120448266</v>
       </c>
       <c r="B41" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4784,21 +4784,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446336</v>
+        <v>446452</v>
       </c>
       <c r="R41" t="n">
-        <v>6997477</v>
+        <v>6997136</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4844,6 +4844,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4870,7 +4875,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120448274</v>
+        <v>120448245</v>
       </c>
       <c r="B42" t="n">
         <v>57320</v>
@@ -4910,10 +4915,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>446287</v>
+        <v>446402</v>
       </c>
       <c r="R42" t="n">
-        <v>6997154</v>
+        <v>6997470</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4977,7 +4982,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120448249</v>
+        <v>120448261</v>
       </c>
       <c r="B43" t="n">
         <v>57320</v>
@@ -5017,10 +5022,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446429</v>
+        <v>446602</v>
       </c>
       <c r="R43" t="n">
-        <v>6997196</v>
+        <v>6997097</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5084,10 +5089,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120448297</v>
+        <v>120448269</v>
       </c>
       <c r="B44" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5100,21 +5105,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5124,10 +5129,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446370</v>
+        <v>446425</v>
       </c>
       <c r="R44" t="n">
-        <v>6997167</v>
+        <v>6997128</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5160,6 +5165,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5186,10 +5196,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120448302</v>
+        <v>120448242</v>
       </c>
       <c r="B45" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5202,21 +5212,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5226,10 +5236,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446778</v>
+        <v>446301</v>
       </c>
       <c r="R45" t="n">
-        <v>6997056</v>
+        <v>6997407</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5266,7 +5276,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5293,10 +5303,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120448303</v>
+        <v>120448297</v>
       </c>
       <c r="B46" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5309,21 +5319,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5333,10 +5343,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>446788</v>
+        <v>446370</v>
       </c>
       <c r="R46" t="n">
-        <v>6997029</v>
+        <v>6997167</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,10 +5405,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120448287</v>
+        <v>120448300</v>
       </c>
       <c r="B47" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5411,21 +5421,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5435,10 +5445,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>446425</v>
+        <v>446471</v>
       </c>
       <c r="R47" t="n">
-        <v>6997299</v>
+        <v>6997266</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5497,10 +5507,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120448231</v>
+        <v>120448256</v>
       </c>
       <c r="B48" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5513,21 +5523,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5537,10 +5547,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>446466</v>
+        <v>446770</v>
       </c>
       <c r="R48" t="n">
-        <v>6997357</v>
+        <v>6997084</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5573,6 +5583,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5599,7 +5614,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120448266</v>
+        <v>120448270</v>
       </c>
       <c r="B49" t="n">
         <v>57320</v>
@@ -5639,10 +5654,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>446452</v>
+        <v>446366</v>
       </c>
       <c r="R49" t="n">
-        <v>6997136</v>
+        <v>6997164</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5679,7 +5694,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5706,7 +5721,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120448236</v>
+        <v>120448253</v>
       </c>
       <c r="B50" t="n">
         <v>57320</v>
@@ -5746,10 +5761,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>446454</v>
+        <v>446684</v>
       </c>
       <c r="R50" t="n">
-        <v>6997366</v>
+        <v>6997177</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5786,7 +5801,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5813,7 +5828,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120448246</v>
+        <v>120448254</v>
       </c>
       <c r="B51" t="n">
         <v>57320</v>
@@ -5853,10 +5868,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>446441</v>
+        <v>446704</v>
       </c>
       <c r="R51" t="n">
-        <v>6997402</v>
+        <v>6997139</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5920,10 +5935,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120448283</v>
+        <v>120448275</v>
       </c>
       <c r="B52" t="n">
-        <v>57341</v>
+        <v>57473</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5932,25 +5947,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100110</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5960,10 +5975,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>446809</v>
+        <v>446646</v>
       </c>
       <c r="R52" t="n">
-        <v>6997041</v>
+        <v>6997094</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5996,6 +6011,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6022,10 +6042,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120448305</v>
+        <v>120448292</v>
       </c>
       <c r="B53" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6038,21 +6058,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6062,10 +6082,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>446347</v>
+        <v>446681</v>
       </c>
       <c r="R53" t="n">
-        <v>6997159</v>
+        <v>6997178</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6124,10 +6144,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120448237</v>
+        <v>120448294</v>
       </c>
       <c r="B54" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6140,21 +6160,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6164,10 +6184,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446537</v>
+        <v>446688</v>
       </c>
       <c r="R54" t="n">
-        <v>6997341</v>
+        <v>6997158</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6200,11 +6220,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6231,10 +6246,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120448267</v>
+        <v>120448282</v>
       </c>
       <c r="B55" t="n">
-        <v>57320</v>
+        <v>57341</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6243,25 +6258,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6271,10 +6286,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446448</v>
+        <v>446561</v>
       </c>
       <c r="R55" t="n">
-        <v>6997133</v>
+        <v>6997196</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6307,11 +6322,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6338,7 +6348,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120448233</v>
+        <v>120448244</v>
       </c>
       <c r="B56" t="n">
         <v>57320</v>
@@ -6378,10 +6388,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446364</v>
+        <v>446358</v>
       </c>
       <c r="R56" t="n">
-        <v>6997405</v>
+        <v>6997469</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6418,7 +6428,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6445,10 +6455,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120448234</v>
+        <v>120448278</v>
       </c>
       <c r="B57" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6461,21 +6471,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6485,10 +6495,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>446347</v>
+        <v>446466</v>
       </c>
       <c r="R57" t="n">
-        <v>6997438</v>
+        <v>6997354</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6521,11 +6531,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6552,10 +6557,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120448290</v>
+        <v>120448231</v>
       </c>
       <c r="B58" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6568,21 +6573,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6592,10 +6597,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>446532</v>
+        <v>446466</v>
       </c>
       <c r="R58" t="n">
-        <v>6997179</v>
+        <v>6997357</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6654,10 +6659,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120448254</v>
+        <v>120448299</v>
       </c>
       <c r="B59" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6670,21 +6675,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6694,10 +6699,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>446704</v>
+        <v>446445</v>
       </c>
       <c r="R59" t="n">
-        <v>6997139</v>
+        <v>6997400</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6730,11 +6735,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6761,10 +6761,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120448275</v>
+        <v>120448243</v>
       </c>
       <c r="B60" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6777,21 +6777,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6801,10 +6801,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>446646</v>
+        <v>446350</v>
       </c>
       <c r="R60" t="n">
-        <v>6997094</v>
+        <v>6997490</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 38082-2024 artfynd.xlsx
+++ b/artfynd/A 38082-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120448298</v>
+        <v>120448272</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446309</v>
+        <v>446301</v>
       </c>
       <c r="R2" t="n">
-        <v>6997481</v>
+        <v>6997158</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120448272</v>
+        <v>120448240</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446301</v>
+        <v>446404</v>
       </c>
       <c r="R3" t="n">
-        <v>6997158</v>
+        <v>6997319</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120448240</v>
+        <v>120448258</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446404</v>
+        <v>446658</v>
       </c>
       <c r="R4" t="n">
-        <v>6997319</v>
+        <v>6997074</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120448258</v>
+        <v>120448273</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446658</v>
+        <v>446289</v>
       </c>
       <c r="R5" t="n">
-        <v>6997074</v>
+        <v>6997154</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120448273</v>
+        <v>120448248</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446289</v>
+        <v>446537</v>
       </c>
       <c r="R6" t="n">
-        <v>6997154</v>
+        <v>6997277</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120448248</v>
+        <v>120448298</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446537</v>
+        <v>446309</v>
       </c>
       <c r="R7" t="n">
-        <v>6997277</v>
+        <v>6997481</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -6557,10 +6557,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120448231</v>
+        <v>120448299</v>
       </c>
       <c r="B58" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6573,21 +6573,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6597,10 +6597,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>446466</v>
+        <v>446445</v>
       </c>
       <c r="R58" t="n">
-        <v>6997357</v>
+        <v>6997400</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6659,10 +6659,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120448299</v>
+        <v>120448231</v>
       </c>
       <c r="B59" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6675,21 +6675,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6699,10 +6699,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>446445</v>
+        <v>446466</v>
       </c>
       <c r="R59" t="n">
-        <v>6997400</v>
+        <v>6997357</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
